--- a/26/Instancias_Excel/instancia.xlsx
+++ b/26/Instancias_Excel/instancia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Proyecto_Opti\26\Instancias_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD1D2ED-B027-4329-97B7-2F21AE35E24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869ED74D-7414-4CD6-9A96-B5693F3C1843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4808,7 +4808,7 @@
         <v>86</v>
       </c>
       <c r="B5">
-        <v>2000000000</v>
+        <v>1700000000</v>
       </c>
     </row>
   </sheetData>
